--- a/data/analysis-data/20260826_panel_eaae_2020_2024_industria_escenario_devaluacion.xlsx
+++ b/data/analysis-data/20260826_panel_eaae_2020_2024_industria_escenario_devaluacion.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>El escenario se actualiza desde el panel CSV ya validado: 20260824_panel_eaae_2020_2024_industria.csv . No se recalcula el panel porque los nuevos coeficientes son parametros de modelamiento de devaluación y no modifican variables base EAAE.</t>
+          <t>El escenario se actualiza desde el panel CSV ya validado: 20260826_panel_eaae_2020_2024_industria.csv . No se recalcula el panel porque los nuevos coeficientes son parametros de modelamiento de devaluación y no modifican variables base EAAE.</t>
         </is>
       </c>
     </row>
@@ -125,7 +125,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>La serie de intereses disponible es anual y corresponde a la industria manufacturera agregada. No existe en la fuente disponible una apertura directa por subrama ni por los grupos exportadora y mercado interno.</t>
+          <t>La serie de intereses disponible es anual y corresponde a la industria manufacturera agregada. La apertura entre grupos exportadora y mercado interno se toma de microdatos del CIU.</t>
         </is>
       </c>
     </row>
@@ -142,7 +142,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Para los grupos de subramas, los intereses industriales se asignan proporcionalmente por participación en el valor bruto de producción a precios productor de cada grupo dentro del total industrial del mismo año.</t>
+          <t>Para los grupos de subramas, los intereses industriales se asignan según microdatos del CIU: 65,6% para ramas exportadoras y 34,4% para ramas orientadas al mercado interno. La industria total conserva el 100% de la serie agregada.</t>
         </is>
       </c>
     </row>
@@ -159,7 +159,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>intereses_grupo = intereses_industria_total * (vbp_pp_grupo / vbp_pp_industria_total)</t>
+          <t>intereses_grupo = intereses_industria_total * participacion_CIU; participacion_CIU exportadora = 0,656; participacion_CIU mercado-interno = 0,344.</t>
         </is>
       </c>
     </row>
@@ -898,30 +898,35 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
+          <t>participacion_intereses_industria</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>intereses_industria_pesos</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>metodo_intereses</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ganancia_pb_desp_intereses</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ganancia_pp_desp_intereses</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>tasa_ganancia_pb_desp_intereses</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>tasa_ganancia_pp_desp_intereses</t>
         </is>
@@ -1017,23 +1022,26 @@
         <v>95.8089154966409</v>
       </c>
       <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
         <v>4023974450.85892</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>intereses_industria_total_convertidos_a_pesos_con_tcc</t>
         </is>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <v>49348974095.0328</v>
       </c>
-      <c r="AD2">
+      <c r="AE2">
         <v>80911393987.4998</v>
       </c>
-      <c r="AE2">
+      <c r="AF2">
         <v>0.117128445100253</v>
       </c>
-      <c r="AF2">
+      <c r="AG2">
         <v>0.192040988540098</v>
       </c>
     </row>
@@ -1127,24 +1135,27 @@
         <v>95.8089154966409</v>
       </c>
       <c r="AA3">
-        <v>2714680809.66226</v>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>asignacion_intereses_industria_por_participacion_vbp_pp</t>
-        </is>
-      </c>
-      <c r="AC3">
-        <v>30135592221.0913</v>
+        <v>0.656</v>
+      </c>
+      <c r="AB3">
+        <v>2639727239.76345</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>asignacion_intereses_industria_microdatos_ciu_65_6_exportadora_34_4_mercado_interno</t>
+        </is>
       </c>
       <c r="AD3">
-        <v>40823380824.8493</v>
+        <v>30210545790.9901</v>
       </c>
       <c r="AE3">
-        <v>0.100056664215378</v>
+        <v>40898334394.7482</v>
       </c>
       <c r="AF3">
-        <v>0.135542426953524</v>
+        <v>0.100305526229441</v>
+      </c>
+      <c r="AG3">
+        <v>0.135791288967587</v>
       </c>
     </row>
     <row r="4">
@@ -1237,24 +1248,27 @@
         <v>95.8089154966409</v>
       </c>
       <c r="AA4">
-        <v>815791720.612211</v>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>asignacion_intereses_industria_por_participacion_vbp_pp</t>
-        </is>
-      </c>
-      <c r="AC4">
-        <v>18376648052.5259</v>
+        <v>0.344</v>
+      </c>
+      <c r="AB4">
+        <v>1384247211.09547</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>asignacion_intereses_industria_microdatos_ciu_65_6_exportadora_34_4_mercado_interno</t>
+        </is>
       </c>
       <c r="AD4">
-        <v>18448561934.2349</v>
+        <v>17808192562.0427</v>
       </c>
       <c r="AE4">
-        <v>0.214487651082634</v>
+        <v>17880106443.7517</v>
       </c>
       <c r="AF4">
-        <v>0.215327011967378</v>
+        <v>0.207852780427753</v>
+      </c>
+      <c r="AG4">
+        <v>0.208692141312497</v>
       </c>
     </row>
     <row r="5">
@@ -1347,23 +1361,26 @@
         <v>78.2759304816489</v>
       </c>
       <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
         <v>3409699531.78063</v>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>intereses_industria_total_convertidos_a_pesos_con_tcc</t>
         </is>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <v>104771177622.558</v>
       </c>
-      <c r="AD5">
+      <c r="AE5">
         <v>115703547962.951</v>
       </c>
-      <c r="AE5">
+      <c r="AF5">
         <v>0.200129809304199</v>
       </c>
-      <c r="AF5">
+      <c r="AG5">
         <v>0.221012395919266</v>
       </c>
     </row>
@@ -1457,24 +1474,27 @@
         <v>78.2759304816489</v>
       </c>
       <c r="AA6">
-        <v>2353144540.32167</v>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>asignacion_intereses_industria_por_participacion_vbp_pp</t>
-        </is>
-      </c>
-      <c r="AC6">
-        <v>76754422370.9182</v>
+        <v>0.656</v>
+      </c>
+      <c r="AB6">
+        <v>2236762892.84809</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>asignacion_intereses_industria_microdatos_ciu_65_6_exportadora_34_4_mercado_interno</t>
+        </is>
       </c>
       <c r="AD6">
-        <v>87585542549.6647</v>
+        <v>76870804018.3918</v>
       </c>
       <c r="AE6">
-        <v>0.19659215587115</v>
+        <v>87701924197.1383</v>
       </c>
       <c r="AF6">
-        <v>0.224334052698271</v>
+        <v>0.196890245782766</v>
+      </c>
+      <c r="AG6">
+        <v>0.224632142609887</v>
       </c>
     </row>
     <row r="7">
@@ -1567,24 +1587,27 @@
         <v>78.2759304816489</v>
       </c>
       <c r="AA7">
-        <v>689888686.708565</v>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>asignacion_intereses_industria_por_participacion_vbp_pp</t>
-        </is>
-      </c>
-      <c r="AC7">
-        <v>20950945632.3904</v>
+        <v>0.344</v>
+      </c>
+      <c r="AB7">
+        <v>1172936638.93254</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>asignacion_intereses_industria_microdatos_ciu_65_6_exportadora_34_4_mercado_interno</t>
+        </is>
       </c>
       <c r="AD7">
-        <v>21052195794.0366</v>
+        <v>20467897680.1665</v>
       </c>
       <c r="AE7">
-        <v>0.214732073430551</v>
+        <v>20569147841.8126</v>
       </c>
       <c r="AF7">
-        <v>0.215769814519996</v>
+        <v>0.209781180512998</v>
+      </c>
+      <c r="AG7">
+        <v>0.210818921602443</v>
       </c>
     </row>
     <row r="8">
@@ -1677,23 +1700,26 @@
         <v>102.429473674941</v>
       </c>
       <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
         <v>4230337262.77507</v>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>intereses_industria_total_convertidos_a_pesos_con_tcc</t>
         </is>
       </c>
-      <c r="AC8">
+      <c r="AD8">
         <v>103945545051.224</v>
       </c>
-      <c r="AD8">
+      <c r="AE8">
         <v>144172357237.828</v>
       </c>
-      <c r="AE8">
+      <c r="AF8">
         <v>0.181372294849602</v>
       </c>
-      <c r="AF8">
+      <c r="AG8">
         <v>0.251563174479632</v>
       </c>
     </row>
@@ -1787,24 +1813,27 @@
         <v>102.429473674941</v>
       </c>
       <c r="AA9">
-        <v>2820496775.25218</v>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>asignacion_intereses_industria_por_participacion_vbp_pp</t>
-        </is>
-      </c>
-      <c r="AC9">
-        <v>71070827752.4241</v>
+        <v>0.656</v>
+      </c>
+      <c r="AB9">
+        <v>2775101244.38045</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>asignacion_intereses_industria_microdatos_ciu_65_6_exportadora_34_4_mercado_interno</t>
+        </is>
       </c>
       <c r="AD9">
-        <v>83646846840.5782</v>
+        <v>71116223283.2959</v>
       </c>
       <c r="AE9">
-        <v>0.169064954341697</v>
+        <v>83692242371.45</v>
       </c>
       <c r="AF9">
-        <v>0.198981083929291</v>
+        <v>0.169172942296767</v>
+      </c>
+      <c r="AG9">
+        <v>0.199089071884361</v>
       </c>
     </row>
     <row r="10">
@@ -1897,24 +1926,27 @@
         <v>102.429473674941</v>
       </c>
       <c r="AA10">
-        <v>935194916.737174</v>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>asignacion_intereses_industria_por_participacion_vbp_pp</t>
-        </is>
-      </c>
-      <c r="AC10">
-        <v>23074138891.877</v>
+        <v>0.344</v>
+      </c>
+      <c r="AB10">
+        <v>1455236018.39463</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>asignacion_intereses_industria_microdatos_ciu_65_6_exportadora_34_4_mercado_interno</t>
+        </is>
       </c>
       <c r="AD10">
-        <v>23247038239.3268</v>
+        <v>22554097790.2196</v>
       </c>
       <c r="AE10">
-        <v>0.197552697645264</v>
+        <v>22726997137.6694</v>
       </c>
       <c r="AF10">
-        <v>0.199033001316394</v>
+        <v>0.193100287828358</v>
+      </c>
+      <c r="AG10">
+        <v>0.194580591499488</v>
       </c>
     </row>
     <row r="11">
@@ -2007,23 +2039,26 @@
         <v>144.245481997278</v>
       </c>
       <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
         <v>5581578925.88468</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>intereses_industria_total_convertidos_a_pesos_con_tcc</t>
         </is>
       </c>
-      <c r="AC11">
+      <c r="AD11">
         <v>63552970478.4843</v>
       </c>
-      <c r="AD11">
+      <c r="AE11">
         <v>105241457177.129</v>
       </c>
-      <c r="AE11">
+      <c r="AF11">
         <v>0.111027242545278</v>
       </c>
-      <c r="AF11">
+      <c r="AG11">
         <v>0.183857162046886</v>
       </c>
     </row>
@@ -2117,24 +2152,27 @@
         <v>144.245481997278</v>
       </c>
       <c r="AA12">
-        <v>3730773815.35718</v>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>asignacion_intereses_industria_por_participacion_vbp_pp</t>
-        </is>
-      </c>
-      <c r="AC12">
-        <v>43156600728.5425</v>
+        <v>0.656</v>
+      </c>
+      <c r="AB12">
+        <v>3661515775.38035</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>asignacion_intereses_industria_microdatos_ciu_65_6_exportadora_34_4_mercado_interno</t>
+        </is>
       </c>
       <c r="AD12">
-        <v>56033441588.6126</v>
+        <v>43225858768.5193</v>
       </c>
       <c r="AE12">
-        <v>0.101946929182778</v>
+        <v>56102699628.5894</v>
       </c>
       <c r="AF12">
-        <v>0.132365320833148</v>
+        <v>0.102110534387489</v>
+      </c>
+      <c r="AG12">
+        <v>0.13252892603786</v>
       </c>
     </row>
     <row r="13">
@@ -2227,24 +2265,27 @@
         <v>144.245481997278</v>
       </c>
       <c r="AA13">
-        <v>1200543903.62774</v>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>asignacion_intereses_industria_por_participacion_vbp_pp</t>
-        </is>
-      </c>
-      <c r="AC13">
-        <v>14615469280.8416</v>
+        <v>0.344</v>
+      </c>
+      <c r="AB13">
+        <v>1920063150.50433</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>asignacion_intereses_industria_microdatos_ciu_65_6_exportadora_34_4_mercado_interno</t>
+        </is>
       </c>
       <c r="AD13">
-        <v>14822023979.4166</v>
+        <v>13895950033.965</v>
       </c>
       <c r="AE13">
-        <v>0.129780925204668</v>
+        <v>14102504732.54</v>
       </c>
       <c r="AF13">
-        <v>0.13161506815084</v>
+        <v>0.123391812972424</v>
+      </c>
+      <c r="AG13">
+        <v>0.125225955918596</v>
       </c>
     </row>
     <row r="14">
@@ -2337,23 +2378,26 @@
         <v>140.859455712867</v>
       </c>
       <c r="AA14">
+        <v>1</v>
+      </c>
+      <c r="AB14">
         <v>5667480200.60721</v>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>intereses_industria_total_convertidos_a_pesos_con_tcc</t>
         </is>
       </c>
-      <c r="AC14">
+      <c r="AD14">
         <v>72493212978.9227</v>
       </c>
-      <c r="AD14">
+      <c r="AE14">
         <v>117862820315.926</v>
       </c>
-      <c r="AE14">
+      <c r="AF14">
         <v>0.11756190155149</v>
       </c>
-      <c r="AF14">
+      <c r="AG14">
         <v>0.191137579770269</v>
       </c>
     </row>
@@ -2447,24 +2491,27 @@
         <v>140.859455712867</v>
       </c>
       <c r="AA15">
-        <v>3887276234.61581</v>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>asignacion_intereses_industria_por_participacion_vbp_pp</t>
-        </is>
-      </c>
-      <c r="AC15">
-        <v>62321852767.5569</v>
+        <v>0.656</v>
+      </c>
+      <c r="AB15">
+        <v>3717867011.59833</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>asignacion_intereses_industria_microdatos_ciu_65_6_exportadora_34_4_mercado_interno</t>
+        </is>
       </c>
       <c r="AD15">
-        <v>75650051375.0985</v>
+        <v>62491261990.5744</v>
       </c>
       <c r="AE15">
-        <v>0.135467576435219</v>
+        <v>75819460598.116</v>
       </c>
       <c r="AF15">
-        <v>0.164438774874153</v>
+        <v>0.13583581736274</v>
+      </c>
+      <c r="AG15">
+        <v>0.164807015801674</v>
       </c>
     </row>
     <row r="16">
@@ -2557,24 +2604,27 @@
         <v>140.859455712867</v>
       </c>
       <c r="AA16">
-        <v>1209972004.56652</v>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>asignacion_intereses_industria_por_participacion_vbp_pp</t>
-        </is>
-      </c>
-      <c r="AC16">
-        <v>19129017406.7906</v>
+        <v>0.344</v>
+      </c>
+      <c r="AB16">
+        <v>1949613189.00888</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>asignacion_intereses_industria_microdatos_ciu_65_6_exportadora_34_4_mercado_interno</t>
+        </is>
       </c>
       <c r="AD16">
-        <v>19313717185.2527</v>
+        <v>18389376222.3483</v>
       </c>
       <c r="AE16">
-        <v>0.16329923446815</v>
+        <v>18574076000.8103</v>
       </c>
       <c r="AF16">
-        <v>0.164875966392634</v>
+        <v>0.156985118241894</v>
+      </c>
+      <c r="AG16">
+        <v>0.158561850166378</v>
       </c>
     </row>
   </sheetData>
@@ -3377,49 +3427,49 @@
         <v>13.0438203564827</v>
       </c>
       <c r="BA3">
-        <v>2714680809.66226</v>
+        <v>2639727239.76345</v>
       </c>
       <c r="BB3">
-        <v>2800115769.17262</v>
+        <v>2722803301.24548</v>
       </c>
       <c r="BC3">
-        <v>85434959.5103621</v>
+        <v>83076061.4820305</v>
       </c>
       <c r="BD3">
-        <v>30135592221.0913</v>
+        <v>30210545790.9901</v>
       </c>
       <c r="BE3">
-        <v>70761526319.3488</v>
+        <v>70838838787.276</v>
       </c>
       <c r="BF3">
-        <v>134.810471950255</v>
+        <v>134.483809982681</v>
       </c>
       <c r="BG3">
-        <v>40823380824.8493</v>
+        <v>40898334394.7482</v>
       </c>
       <c r="BH3">
-        <v>81449314923.1069</v>
+        <v>81526627391.034</v>
       </c>
       <c r="BI3">
-        <v>99.5163391110625</v>
+        <v>99.3397251930705</v>
       </c>
       <c r="BJ3">
-        <v>0.100056664215378</v>
+        <v>0.100305526229441</v>
       </c>
       <c r="BK3">
-        <v>0.230968825627567</v>
+        <v>0.231221177023195</v>
       </c>
       <c r="BL3">
-        <v>13.0912161412189</v>
+        <v>13.0915650793755</v>
       </c>
       <c r="BM3">
-        <v>0.135542426953524</v>
+        <v>0.135791288967587</v>
       </c>
       <c r="BN3">
-        <v>0.265854251518821</v>
+        <v>0.26610660291445</v>
       </c>
       <c r="BO3">
-        <v>13.0311824565297</v>
+        <v>13.0315313946863</v>
       </c>
     </row>
     <row r="4">
@@ -3588,49 +3638,49 @@
         <v>-3.22712647517522</v>
       </c>
       <c r="BA4">
-        <v>815791720.612211</v>
+        <v>1384247211.09547</v>
       </c>
       <c r="BB4">
-        <v>841465874.41008</v>
+        <v>1427811487.23848</v>
       </c>
       <c r="BC4">
-        <v>25674153.7978692</v>
+        <v>43564276.143016</v>
       </c>
       <c r="BD4">
-        <v>18376648052.5259</v>
+        <v>17808192562.0427</v>
       </c>
       <c r="BE4">
-        <v>16141724413.7627</v>
+        <v>15555378800.9343</v>
       </c>
       <c r="BF4">
-        <v>-12.1617589474163</v>
+        <v>-12.6504346427059</v>
       </c>
       <c r="BG4">
-        <v>18448561934.2349</v>
+        <v>17880106443.7517</v>
       </c>
       <c r="BH4">
-        <v>16213638295.4717</v>
+        <v>15627292682.6432</v>
       </c>
       <c r="BI4">
-        <v>-12.114351496503</v>
+        <v>-12.5995545283551</v>
       </c>
       <c r="BJ4">
-        <v>0.214487651082634</v>
+        <v>0.207852780427753</v>
       </c>
       <c r="BK4">
-        <v>0.182264050194273</v>
+        <v>0.175643337098922</v>
       </c>
       <c r="BL4">
-        <v>-3.22236008883602</v>
+        <v>-3.22094433288303</v>
       </c>
       <c r="BM4">
-        <v>0.215327011967378</v>
+        <v>0.208692141312497</v>
       </c>
       <c r="BN4">
-        <v>0.183076064760344</v>
+        <v>0.176455351664993</v>
       </c>
       <c r="BO4">
-        <v>-3.22509472070335</v>
+        <v>-3.22367896475036</v>
       </c>
     </row>
     <row r="5">
@@ -4010,49 +4060,49 @@
         <v>12.4916211852635</v>
       </c>
       <c r="BA6">
-        <v>2353144540.32167</v>
+        <v>2236762892.84809</v>
       </c>
       <c r="BB6">
-        <v>2423682306.93657</v>
+        <v>2303812007.85359</v>
       </c>
       <c r="BC6">
-        <v>70537766.6149007</v>
+        <v>67049115.0054987</v>
       </c>
       <c r="BD6">
-        <v>76754422370.9182</v>
+        <v>76870804018.3918</v>
       </c>
       <c r="BE6">
-        <v>127545903782.544</v>
+        <v>127665774081.627</v>
       </c>
       <c r="BF6">
-        <v>66.1740129658905</v>
+        <v>66.0783644868371</v>
       </c>
       <c r="BG6">
-        <v>87585542549.6647</v>
+        <v>87701924197.1383</v>
       </c>
       <c r="BH6">
-        <v>138377023961.29</v>
+        <v>138496894260.373</v>
       </c>
       <c r="BI6">
-        <v>57.9907139158552</v>
+        <v>57.9177372996482</v>
       </c>
       <c r="BJ6">
-        <v>0.19659215587115</v>
+        <v>0.196890245782766</v>
       </c>
       <c r="BK6">
-        <v>0.321832035073627</v>
+        <v>0.322134499528813</v>
       </c>
       <c r="BL6">
-        <v>12.5239879202477</v>
+        <v>12.5244253746047</v>
       </c>
       <c r="BM6">
-        <v>0.224334052698271</v>
+        <v>0.224632142609887</v>
       </c>
       <c r="BN6">
-        <v>0.349161814751977</v>
+        <v>0.349464279207163</v>
       </c>
       <c r="BO6">
-        <v>12.4827762053706</v>
+        <v>12.4832136597276</v>
       </c>
     </row>
     <row r="7">
@@ -4221,49 +4271,49 @@
         <v>-3.65638445135217</v>
       </c>
       <c r="BA7">
-        <v>689888686.708565</v>
+        <v>1172936638.93254</v>
       </c>
       <c r="BB7">
-        <v>710568762.385793</v>
+        <v>1208096540.70371</v>
       </c>
       <c r="BC7">
-        <v>20680075.6772285</v>
+        <v>35159901.7711761</v>
       </c>
       <c r="BD7">
-        <v>20950945632.3904</v>
+        <v>20467897680.1665</v>
       </c>
       <c r="BE7">
-        <v>18005054502.7176</v>
+        <v>17507526724.3997</v>
       </c>
       <c r="BF7">
-        <v>-14.0608981635581</v>
+        <v>-14.4634832654817</v>
       </c>
       <c r="BG7">
-        <v>21052195794.0366</v>
+        <v>20569147841.8126</v>
       </c>
       <c r="BH7">
-        <v>18106304664.3638</v>
+        <v>17608776886.0458</v>
       </c>
       <c r="BI7">
-        <v>-13.9932725236544</v>
+        <v>-14.3922878017776</v>
       </c>
       <c r="BJ7">
-        <v>0.214732073430551</v>
+        <v>0.209781180512998</v>
       </c>
       <c r="BK7">
-        <v>0.178240264576486</v>
+        <v>0.173315009680526</v>
       </c>
       <c r="BL7">
-        <v>-3.64918088540645</v>
+        <v>-3.64661708324717</v>
       </c>
       <c r="BM7">
-        <v>0.215769814519996</v>
+        <v>0.210818921602443</v>
       </c>
       <c r="BN7">
-        <v>0.179242586207754</v>
+        <v>0.174317331311794</v>
       </c>
       <c r="BO7">
-        <v>-3.65272283122419</v>
+        <v>-3.65015902906492</v>
       </c>
     </row>
     <row r="8">
@@ -4643,49 +4693,49 @@
         <v>15.0971650964065</v>
       </c>
       <c r="BA9">
-        <v>2820496775.25218</v>
+        <v>2775101244.38045</v>
       </c>
       <c r="BB9">
-        <v>2917872649.83943</v>
+        <v>2870909866.85815</v>
       </c>
       <c r="BC9">
-        <v>97375874.5872483</v>
+        <v>95808622.4777004</v>
       </c>
       <c r="BD9">
-        <v>71070827752.4241</v>
+        <v>71116223283.2959</v>
       </c>
       <c r="BE9">
-        <v>137300990488.337</v>
+        <v>137347953271.318</v>
       </c>
       <c r="BF9">
-        <v>93.1889564683647</v>
+        <v>93.1316750668611</v>
       </c>
       <c r="BG9">
-        <v>83646846840.5782</v>
+        <v>83692242371.45</v>
       </c>
       <c r="BH9">
-        <v>149877009576.491</v>
+        <v>149923972359.473</v>
       </c>
       <c r="BI9">
-        <v>79.1783136334361</v>
+        <v>79.1372391410751</v>
       </c>
       <c r="BJ9">
-        <v>0.169064954341697</v>
+        <v>0.169172942296767</v>
       </c>
       <c r="BK9">
-        <v>0.320495506530993</v>
+        <v>0.320605129636159</v>
       </c>
       <c r="BL9">
-        <v>15.1430552189296</v>
+        <v>15.1432187339392</v>
       </c>
       <c r="BM9">
-        <v>0.198981083929291</v>
+        <v>0.199089071884361</v>
       </c>
       <c r="BN9">
-        <v>0.349851140408549</v>
+        <v>0.349960763513715</v>
       </c>
       <c r="BO9">
-        <v>15.0870056479258</v>
+        <v>15.0871691629354</v>
       </c>
     </row>
     <row r="10">
@@ -4854,49 +4904,49 @@
         <v>-5.18562778108301</v>
       </c>
       <c r="BA10">
-        <v>935194916.737174</v>
+        <v>1455236018.39463</v>
       </c>
       <c r="BB10">
-        <v>967481932.175683</v>
+        <v>1505477125.30366</v>
       </c>
       <c r="BC10">
-        <v>32287015.4385087</v>
+        <v>50241106.909038</v>
       </c>
       <c r="BD10">
-        <v>23074138891.877</v>
+        <v>22554097790.2196</v>
       </c>
       <c r="BE10">
-        <v>17822640753.2735</v>
+        <v>17284645560.1456</v>
       </c>
       <c r="BF10">
-        <v>-22.7592377908941</v>
+        <v>-23.363613473198</v>
       </c>
       <c r="BG10">
-        <v>23247038239.3268</v>
+        <v>22726997137.6694</v>
       </c>
       <c r="BH10">
-        <v>17995540100.7234</v>
+        <v>17457544907.5954</v>
       </c>
       <c r="BI10">
-        <v>-22.5899664487993</v>
+        <v>-23.1858709628648</v>
       </c>
       <c r="BJ10">
-        <v>0.197552697645264</v>
+        <v>0.193100287828358</v>
       </c>
       <c r="BK10">
-        <v>0.145851246118841</v>
+        <v>0.141448572552678</v>
       </c>
       <c r="BL10">
-        <v>-5.17014515264223</v>
+        <v>-5.16517152756797</v>
       </c>
       <c r="BM10">
-        <v>0.199033001316394</v>
+        <v>0.194580591499488</v>
       </c>
       <c r="BN10">
-        <v>0.147266164683816</v>
+        <v>0.142863491117653</v>
       </c>
       <c r="BO10">
-        <v>-5.17668366325774</v>
+        <v>-5.17171003818349</v>
       </c>
     </row>
     <row r="11">
@@ -5276,49 +5326,49 @@
         <v>18.3070990568629</v>
       </c>
       <c r="BA12">
-        <v>3730773815.35718</v>
+        <v>3661515775.38035</v>
       </c>
       <c r="BB12">
-        <v>3904810460.51531</v>
+        <v>3832321606.3631</v>
       </c>
       <c r="BC12">
-        <v>174036645.158128</v>
+        <v>170805830.982747</v>
       </c>
       <c r="BD12">
-        <v>43156600728.5425</v>
+        <v>43225858768.5193</v>
       </c>
       <c r="BE12">
-        <v>123822132177.434</v>
+        <v>123894621031.586</v>
       </c>
       <c r="BF12">
-        <v>186.913542974069</v>
+        <v>186.621537573284</v>
       </c>
       <c r="BG12">
-        <v>56033441588.6126</v>
+        <v>56102699628.5894</v>
       </c>
       <c r="BH12">
-        <v>136698973037.504</v>
+        <v>136771461891.656</v>
       </c>
       <c r="BI12">
-        <v>143.959623328375</v>
+        <v>143.787665829112</v>
       </c>
       <c r="BJ12">
-        <v>0.101946929182778</v>
+        <v>0.102110534387489</v>
       </c>
       <c r="BK12">
-        <v>0.285548832997788</v>
+        <v>0.285716001074646</v>
       </c>
       <c r="BL12">
-        <v>18.360190381501</v>
+        <v>18.3605466687156</v>
       </c>
       <c r="BM12">
-        <v>0.132365320833148</v>
+        <v>0.13252892603786</v>
       </c>
       <c r="BN12">
-        <v>0.315244387545518</v>
+        <v>0.315411555622376</v>
       </c>
       <c r="BO12">
-        <v>18.287906671237</v>
+        <v>18.2882629584516</v>
       </c>
     </row>
     <row r="13">
@@ -5487,49 +5537,49 @@
         <v>-6.19375854874819</v>
       </c>
       <c r="BA13">
-        <v>1200543903.62774</v>
+        <v>1920063150.50433</v>
       </c>
       <c r="BB13">
-        <v>1256548004.57118</v>
+        <v>2009632061.87333</v>
       </c>
       <c r="BC13">
-        <v>56004100.943442</v>
+        <v>89568911.3690014</v>
       </c>
       <c r="BD13">
-        <v>14615469280.8416</v>
+        <v>13895950033.965</v>
       </c>
       <c r="BE13">
-        <v>8115398646.34743</v>
+        <v>7362314589.04528</v>
       </c>
       <c r="BF13">
-        <v>-44.4739098662719</v>
+        <v>-47.0182709994635</v>
       </c>
       <c r="BG13">
-        <v>14822023979.4166</v>
+        <v>14102504732.54</v>
       </c>
       <c r="BH13">
-        <v>8321953344.92247</v>
+        <v>7568869287.62032</v>
       </c>
       <c r="BI13">
-        <v>-43.8541365438404</v>
+        <v>-46.3296100149077</v>
       </c>
       <c r="BJ13">
-        <v>0.129780925204668</v>
+        <v>0.123391812972424</v>
       </c>
       <c r="BK13">
-        <v>0.0680664383536568</v>
+        <v>0.0617500820296764</v>
       </c>
       <c r="BL13">
-        <v>-6.17144868510114</v>
+        <v>-6.16417309427479</v>
       </c>
       <c r="BM13">
-        <v>0.13161506815084</v>
+        <v>0.125225955918596</v>
       </c>
       <c r="BN13">
-        <v>0.0697988785294138</v>
+        <v>0.0634825222054334</v>
       </c>
       <c r="BO13">
-        <v>-6.18161896214257</v>
+        <v>-6.17434337131623</v>
       </c>
     </row>
     <row r="14">
@@ -5909,49 +5959,49 @@
         <v>18.1683884999659</v>
       </c>
       <c r="BA15">
-        <v>3887276234.61581</v>
+        <v>3717867011.59833</v>
       </c>
       <c r="BB15">
-        <v>4064142156.24146</v>
+        <v>3887025037.88738</v>
       </c>
       <c r="BC15">
-        <v>176865921.625645</v>
+        <v>169158026.289045</v>
       </c>
       <c r="BD15">
-        <v>62321852767.5569</v>
+        <v>62491261990.5744</v>
       </c>
       <c r="BE15">
-        <v>149496519226.314</v>
+        <v>149673636344.668</v>
       </c>
       <c r="BF15">
-        <v>139.878168872633</v>
+        <v>139.511303783949</v>
       </c>
       <c r="BG15">
-        <v>75650051375.0985</v>
+        <v>75819460598.116</v>
       </c>
       <c r="BH15">
-        <v>162824717833.855</v>
+        <v>163001834952.209</v>
       </c>
       <c r="BI15">
-        <v>115.234114021305</v>
+        <v>114.986803739223</v>
       </c>
       <c r="BJ15">
-        <v>0.135467576435219</v>
+        <v>0.13583581736274</v>
       </c>
       <c r="BK15">
-        <v>0.317620547315745</v>
+        <v>0.317996850632783</v>
       </c>
       <c r="BL15">
-        <v>18.2152970880526</v>
+        <v>18.2161033270043</v>
       </c>
       <c r="BM15">
-        <v>0.164438774874153</v>
+        <v>0.164807015801674</v>
       </c>
       <c r="BN15">
-        <v>0.345937659703169</v>
+        <v>0.346313963020208</v>
       </c>
       <c r="BO15">
-        <v>18.1498884829016</v>
+        <v>18.1506947218534</v>
       </c>
     </row>
     <row r="16">
@@ -6120,49 +6170,49 @@
         <v>-5.91467173107485</v>
       </c>
       <c r="BA16">
-        <v>1209972004.56652</v>
+        <v>1949613189.00888</v>
       </c>
       <c r="BB16">
-        <v>1265024128.67935</v>
+        <v>2038318007.67265</v>
       </c>
       <c r="BC16">
-        <v>55052124.1128206</v>
+        <v>88704818.6637675</v>
       </c>
       <c r="BD16">
-        <v>19129017406.7906</v>
+        <v>18389376222.3483</v>
       </c>
       <c r="BE16">
-        <v>12913728295.4746</v>
+        <v>12140434416.4813</v>
       </c>
       <c r="BF16">
-        <v>-32.4914185561339</v>
+        <v>-33.9812603228638</v>
       </c>
       <c r="BG16">
-        <v>19313717185.2527</v>
+        <v>18574076000.8103</v>
       </c>
       <c r="BH16">
-        <v>13098428073.9367</v>
+        <v>12325134194.9433</v>
       </c>
       <c r="BI16">
-        <v>-32.1806985765631</v>
+        <v>-33.6433521947168</v>
       </c>
       <c r="BJ16">
-        <v>0.16329923446815</v>
+        <v>0.156985118241894</v>
       </c>
       <c r="BK16">
-        <v>0.104344505356123</v>
+        <v>0.0980961961573962</v>
       </c>
       <c r="BL16">
-        <v>-5.89547291120269</v>
+        <v>-5.88889220844977</v>
       </c>
       <c r="BM16">
-        <v>0.164875966392634</v>
+        <v>0.158561850166378</v>
       </c>
       <c r="BN16">
-        <v>0.105836902174613</v>
+        <v>0.0995885929758861</v>
       </c>
       <c r="BO16">
-        <v>-5.90390642180207</v>
+        <v>-5.89732571904915</v>
       </c>
     </row>
   </sheetData>
